--- a/data.mn/public/datasets/life-expectancy-by-sex.xlsx
+++ b/data.mn/public/datasets/life-expectancy-by-sex.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,7 @@
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="6" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,6 +542,9 @@
       <c r="AD1" t="n">
         <v>2024</v>
       </c>
+      <c r="AE1" t="n">
+        <v>2025</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,6 +639,9 @@
       <c r="AD2" t="n">
         <v>77.09999999999999</v>
       </c>
+      <c r="AE2" t="n">
+        <v>77.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -729,6 +736,9 @@
       <c r="AD3" t="n">
         <v>67.90000000000001</v>
       </c>
+      <c r="AE3" t="n">
+        <v>68.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
